--- a/認可仕様書.xlsx
+++ b/認可仕様書.xlsx
@@ -933,7 +933,8 @@
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>create の第2引数は Book モデル（$this-&gt;authorize('create', [Review::class, $book])）。「1書籍につき1ユーザー1件まで」は、このポリシーに加えて reviews テーブルの (user_id, book_id) の複合ユニーク制約でもデータベース側で担保している。</t>
+          <t>投稿（store）・更新（update）は ReviewRequest::authorize() の中でのみ判定し、入力チェック（rules）より先に権限を判定する（権限がない場合は入力内容にかかわらず 403）。編集画面の表示（edit）・削除（destroy）は FormRequest を経由しないため、コントローラー冒頭の $this-&gt;authorize() で判定する。
+create の第2引数は Book モデル（ルートパラメータ {book}）。「1書籍につき1ユーザー1件まで」は、このポリシーに加えて reviews テーブルの (user_id, book_id) の複合ユニーク制約でもデータベース側で担保している。</t>
         </is>
       </c>
     </row>
@@ -948,7 +949,8 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>create の第2引数は Book モデル（$this-&gt;authorize('create', [ReadingPlan::class, $book])）。「進行中の計画は書籍ごとに1ユーザー1件まで」という制約を実現している。</t>
+          <t>作成（store）・更新（update）は ReadingPlanRequest::authorize() の中でのみ判定し、入力チェック（rules）より先に権限を判定する（権限がない場合は入力内容にかかわらず 403）。編集画面の表示（edit）・読了（complete）・削除（destroy）は FormRequest を経由しないため、コントローラー冒頭の $this-&gt;authorize() で判定する。
+create の第2引数は Book モデル（入力された book_id から取得）。「進行中の計画は書籍ごとに1ユーザー1件まで」という制約を実現している。book_id から書籍が特定できない場合（未選択・存在しないIDなど）は判定対象がないため許可し、入力チェック（required・exists）でエラーにする。</t>
         </is>
       </c>
     </row>
@@ -974,7 +976,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>Genre にはポリシーを作成していない。ジャンル削除の制限は「誰が操作できるか」という認可ではなく「書籍に紐づいているか」というデータ整合性の問題のため、GenreController@destroy 内で $genre-&gt;books()-&gt;exists() を確認している。あわせて book_genre.genre_id に restrictOnDelete 制約を設定し、データベース側でも削除を拒否する。</t>
+          <t>Genre にはポリシーを作成していない。ジャンル削除の制限は「誰が操作できるか」という認可ではなく「書籍に紐づいているか」というデータ整合性の問題のため、GenreController@destroy 内で $genre-&gt;books()-&gt;exists() を確認し、紐づきがある場合は削除を中止する（book_genre.genre_id の外部キーは削除時 CASCADE のため、データベース側では削除を拒否しない）。</t>
         </is>
       </c>
     </row>

--- a/認可仕様書.xlsx
+++ b/認可仕様書.xlsx
@@ -527,7 +527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -771,7 +771,8 @@
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>/reading-plans/edit.blade.php（フォーム送信時 → PUT reading-plans.update）</t>
+          <t>/reading-plans/index.blade.php（「編集」リンク → GET reading-plans.edit 表示時）
+/reading-plans/edit.blade.php（フォーム送信時 → PUT reading-plans.update）</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -837,6 +838,33 @@
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>画面に「403 Forbidden」を表示し、処理を中断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>（該当ポリシーなし）</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>/notifications/index.blade.php（「既読にする」ボタン → POST notifications.read）</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>markAsRead（通知の既読化）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>ログインユーザー自身の通知のみ既読にできる。ポリシーは使わず、NotificationController::markAsRead() で auth()-&gt;user()-&gt;notifications()-&gt;findOrFail($id) により、自分宛ての通知の中からだけ探すことで制限している。</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>他人の通知ID・存在しない通知IDを指定した場合は 404 Not Found。対象の通知は変更されない。</t>
         </is>
       </c>
     </row>
